--- a/AAII_Financials/Yearly/INQR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/INQR_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/INQR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/INQR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>INQR</t>
   </si>
@@ -663,8 +663,8 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -697,8 +697,8 @@
       <c r="H7" s="2">
         <v>39263</v>
       </c>
-      <c r="I7" s="2">
-        <v>38898</v>
+      <c r="I7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
@@ -724,8 +724,8 @@
       <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
-        <v>300</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
@@ -751,8 +751,8 @@
       <c r="H9" s="3">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
-        <v>200</v>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
@@ -778,8 +778,8 @@
       <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
@@ -818,8 +818,8 @@
       <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
-        <v>1100</v>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -872,8 +872,8 @@
       <c r="H14" s="3">
         <v>7900</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -936,8 +936,8 @@
       <c r="H17" s="3">
         <v>15000</v>
       </c>
-      <c r="I17" s="3">
-        <v>7400</v>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
@@ -963,8 +963,8 @@
       <c r="H18" s="3">
         <v>-14700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-7100</v>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
@@ -1003,8 +1003,8 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1030,8 +1030,8 @@
       <c r="H21" s="3">
         <v>-14700</v>
       </c>
-      <c r="I21" s="3">
-        <v>-7100</v>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1084,8 +1084,8 @@
       <c r="H23" s="3">
         <v>-14700</v>
       </c>
-      <c r="I23" s="3">
-        <v>-7100</v>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
@@ -1165,8 +1165,8 @@
       <c r="H26" s="3">
         <v>-14700</v>
       </c>
-      <c r="I26" s="3">
-        <v>-7100</v>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
@@ -1192,8 +1192,8 @@
       <c r="H27" s="3">
         <v>-14700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-7100</v>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
@@ -1327,8 +1327,8 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1354,8 +1354,8 @@
       <c r="H33" s="3">
         <v>-14700</v>
       </c>
-      <c r="I33" s="3">
-        <v>-7100</v>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
@@ -1408,8 +1408,8 @@
       <c r="H35" s="3">
         <v>-14700</v>
       </c>
-      <c r="I35" s="3">
-        <v>-7100</v>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
@@ -1440,8 +1440,8 @@
       <c r="H38" s="2">
         <v>39263</v>
       </c>
-      <c r="I38" s="2">
-        <v>38898</v>
+      <c r="I38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
@@ -1493,8 +1493,8 @@
       <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1547,8 +1547,8 @@
       <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1574,8 +1574,8 @@
       <c r="H44" s="3">
         <v>0</v>
       </c>
-      <c r="I44" s="3">
-        <v>0</v>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -1601,8 +1601,8 @@
       <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>300</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1628,8 +1628,8 @@
       <c r="H46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
-        <v>300</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1682,8 +1682,8 @@
       <c r="H48" s="3">
         <v>100</v>
       </c>
-      <c r="I48" s="3">
-        <v>100</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -1844,8 +1844,8 @@
       <c r="H54" s="3">
         <v>500</v>
       </c>
-      <c r="I54" s="3">
-        <v>400</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -1897,8 +1897,8 @@
       <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
-        <v>200</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -1924,8 +1924,8 @@
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -1951,8 +1951,8 @@
       <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
-        <v>200</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -1978,8 +1978,8 @@
       <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
-        <v>400</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2140,8 +2140,8 @@
       <c r="H66" s="3">
         <v>1900</v>
       </c>
-      <c r="I66" s="3">
-        <v>400</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2288,8 +2288,8 @@
       <c r="H72" s="3">
         <v>-28500</v>
       </c>
-      <c r="I72" s="3">
-        <v>-13800</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2396,8 +2396,8 @@
       <c r="H76" s="3">
         <v>-1500</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2455,8 +2455,8 @@
       <c r="H80" s="2">
         <v>39263</v>
       </c>
-      <c r="I80" s="2">
-        <v>38898</v>
+      <c r="I80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
@@ -2482,8 +2482,8 @@
       <c r="H81" s="3">
         <v>-14700</v>
       </c>
-      <c r="I81" s="3">
-        <v>-7100</v>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
@@ -2522,8 +2522,8 @@
       <c r="H83" s="3">
         <v>0</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -2684,8 +2684,8 @@
       <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
-        <v>-2100</v>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -2724,8 +2724,8 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3">
-        <v>-100</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -2805,8 +2805,8 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3">
-        <v>-100</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -2953,8 +2953,8 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-      <c r="I100" s="3">
-        <v>1900</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
@@ -2980,8 +2980,8 @@
       <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>-100</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3007,8 +3007,8 @@
       <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
-        <v>-300</v>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
